--- a/Output/Renewable_Tender_Tracker_V14.xlsx
+++ b/Output/Renewable_Tender_Tracker_V14.xlsx
@@ -22862,7 +22862,7 @@
         </is>
       </c>
       <c r="AY2" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
     </row>
     <row r="3">
@@ -22962,7 +22962,7 @@
         <v>46237.26024921297</v>
       </c>
       <c r="AY3" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>46243.17686518518</v>
       </c>
       <c r="AY4" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46269.31819381945</v>
       </c>
       <c r="AY5" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="R6" s="280" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="S6" s="37" t="n"/>
       <c r="T6" s="37" t="inlineStr">
@@ -23237,7 +23237,7 @@
       <c r="V6" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  | GEM/2026/B/7937631 |  | Hiring of Latest Model of Mahindra Scorpio (4 WD) or equivalent 4WD Not earlier than 2026 Make)
-vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 1 day to go | </t>
+vehicle for 12 Hours duty for NTPC REL officials at 200 MW ISTS Connected Solar PV Project (Block IX) | Renewable Energy | 07/09/2026 4 Hours to go | </t>
         </is>
       </c>
       <c r="W6" s="278">
@@ -23269,14 +23269,14 @@
       <c r="AH6" s="281" t="n"/>
       <c r="AI6" s="281" t="n"/>
       <c r="AX6" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="AY6" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>f3237a45e074d1244d8137eec1934d44417cb404ec6db3244f0b76b687b7dfff</t>
+          <t>8bfbe36e743a765de0a59b13d5bb40aae8bf5da09af0686b4c2ed9f27a6ef23b</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="64" min="1" max="1"/>
@@ -58443,13 +58443,11 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
           <t>NTPC REL</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
           <t>Other</t>
@@ -58466,6 +58464,420 @@
         </is>
       </c>
       <c r="H415" t="inlineStr">
+        <is>
+          <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SECI000274</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/15/0008/26-27</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>50</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVz</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>SECI000276</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0006/25-26</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>SECI000262</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Solar + BESS</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>25</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR1</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>SECI000263</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0003/26-27</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>SECI000264</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/EOI/17/0002/26-27</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRz</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>SECI000270</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/15/0005/26-27</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>SECI000252</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/OP/11/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>88</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>EPC / turnkey / BoS excluded</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/Ymd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>SECI000267</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/MI/00/0001/26-27</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRw</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>SECI000269</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>40</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Capacity below configured minimum</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmR-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>SECI000265</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SECI</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>SECI/C&amp;P/IPP/11/0007/26-27</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Rooftop solar excluded</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://www.seci.co.in/tender-details/YmRy</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>NTPC REL</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Capacity not confirmed</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
         <is>
           <t>https://ntpctender.ntpc.co.in/NITDetails/NITs/30221</t>
         </is>
@@ -60910,7 +61322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J539"/>
+  <dimension ref="A1:J540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="64" min="1" max="1"/>
@@ -61126,7 +61538,7 @@
         </is>
       </c>
       <c r="C13" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46272.3212846069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -63846,15 +64258,36 @@
         </is>
       </c>
       <c r="G539" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46271.31189354166</v>
       </c>
       <c r="H539" s="282" t="n">
-        <v>46271.31189353833</v>
+        <v>46271.31189354166</v>
       </c>
       <c r="I539" t="n">
         <v>5</v>
       </c>
       <c r="J539" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>RUN-20260907074238</t>
+        </is>
+      </c>
+      <c r="G540" s="282" t="n">
+        <v>46272.3212846069</v>
+      </c>
+      <c r="H540" s="282" t="n">
+        <v>46272.3212846069</v>
+      </c>
+      <c r="I540" t="n">
+        <v>5</v>
+      </c>
+      <c r="J540" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
